--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/월별투자수익_2026-03-01_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/월별투자수익_2026-03-01_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>812658482</v>
+        <v>813248713</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>812354100</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>304329</v>
+        <v>894560</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.05</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0449</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>779805037</v>
+        <v>780353521</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>779495066</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>309891</v>
+        <v>858375</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3.01</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0483</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>812327176</v>
+        <v>812923597</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>812029299</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>297780</v>
+        <v>894201</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.05</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0438</v>
+        <v>0.1316</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>786782422</v>
+        <v>787359606</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>786493494</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>288897</v>
+        <v>866081</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3.06</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0438</v>
+        <v>0.1314</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>807736457</v>
+        <v>808308293</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>807419143</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>317286</v>
+        <v>889122</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>3.01</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0476</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="9">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>702981504</v>
+        <v>703486091</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>702712201</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>269234</v>
+        <v>773821</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>3.03</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="10">
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>4702291078</v>
+        <v>4705679821</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>4700503303</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1787417</v>
+        <v>5176160</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>3.03</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.0457</v>
+        <v>0.1325</v>
       </c>
     </row>
   </sheetData>
